--- a/Robot Arm Parts.xlsx
+++ b/Robot Arm Parts.xlsx
@@ -7,6 +7,7 @@
     <sheet name="Great" sheetId="2" r:id="rId2"/>
     <sheet name="Future" sheetId="3" r:id="rId3"/>
     <sheet name="Compare" sheetId="4" r:id="rId4"/>
+    <sheet name="Audit" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -401,21 +402,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H19"/>
-  <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="55.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="70.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
-    <col min="8" max="8" width="80.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Sufficient</v>
       </c>
+      <c r="B1" t="str">
+        <v/>
+      </c>
+      <c r="C1" t="str">
+        <v/>
+      </c>
+      <c r="D1" t="str">
+        <v/>
+      </c>
+      <c r="E1" t="str">
+        <v/>
+      </c>
+      <c r="F1" t="str">
+        <v/>
+      </c>
+      <c r="G1" t="str">
+        <v/>
+      </c>
+      <c r="H1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -424,6 +436,50 @@
       <c r="B2" t="str">
         <v>2026-02-28</v>
       </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v/>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -502,7 +558,7 @@
         <v>20.4</v>
       </c>
       <c r="H6" t="str">
-        <v>Exact ST/SC serial bus board for the leader arm.</v>
+        <v>Exact repo board ASIN. LeRobot requires ST/SC serial bus support and B-channel jumpers during setup. Official board docs list 9-12.6V input, which conflicts with the repo's 5V leader PSU guidance.</v>
       </c>
     </row>
     <row r="7">
@@ -537,26 +593,26 @@
         <v>Leader</v>
       </c>
       <c r="B8" t="str">
-        <v>5V 5A Power Adapter 25W AC 100-240V to DC Wall Power Supply Converter with 5.5x2.5mm/2.1mm Plug</v>
+        <v>Facmogu DC 5V 4A AC to DC Converter, AC 100-240V to DC 5 Volt 4 Amp 20W Power Supply 5V Switching Transformer Power Adapter, Wall Mounted Adapter with with Barrel Connector 5.5x2.5mm &amp; 5.5x2.1mm</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="str">
-        <v>https://www.amazon.ca/MTDZKJG-100-240V-Converter-5-5x2-5mm-Security/dp/B0CJHQNFMG</v>
+        <v>https://www.amazon.ca/Facmogu-Switching-Transformer-Converter-Compatible/dp/B087LY41PV</v>
       </c>
       <c r="E8">
-        <v>26.41</v>
+        <v>14.39</v>
       </c>
       <c r="F8">
-        <v>5.51</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <f>C8*E8+F8</f>
-        <v>31.92</v>
+        <v>14.39</v>
       </c>
       <c r="H8" t="str">
-        <v>Leader-side power supply with 5.5x2.1mm compatibility.</v>
+        <v>Exact SO-101 repo PSU ASIN. Upstream controller-board voltage guidance conflicts with the repo's 5V leader supply recommendation.</v>
       </c>
     </row>
     <row r="9">
@@ -583,7 +639,7 @@
         <v>199.77</v>
       </c>
       <c r="H9" t="str">
-        <v>Buy 3 packs to get the 6x 12V follower servos required for the shared 12V rail.</v>
+        <v>Buy 3 packs to get the 6x 12V follower servos required for the shared 12V rail. Listing explicitly says 2 servos; accessory/cable contents are not explicit.</v>
       </c>
     </row>
     <row r="10">
@@ -610,7 +666,7 @@
         <v>20.4</v>
       </c>
       <c r="H10" t="str">
-        <v>Exact ST/SC serial bus board for the follower arm.</v>
+        <v>Exact repo board ASIN. Set jumpers to B-channel (USB) during LeRobot motor setup. Works with ST/SC serial bus servos.</v>
       </c>
     </row>
     <row r="11">
@@ -691,7 +747,7 @@
         <v>7.33</v>
       </c>
       <c r="H13" t="str">
-        <v>Arm hardware fill-in for M2x6 requirements.</v>
+        <v>Matches LeRobot's M2x6 requirement for the arms. Two-arm build needs about 47 M2x6 screws from the HF assembly steps.</v>
       </c>
     </row>
     <row r="14">
@@ -718,7 +774,7 @@
         <v>10.49</v>
       </c>
       <c r="H14" t="str">
-        <v>Arm hardware fill-in including M3x6 screws.</v>
+        <v>Current Amazon-only placeholder. Local LeRobot assembly docs call for M3x6 pan-head screws; this row is not an exact head-type match.</v>
       </c>
     </row>
     <row r="15">
@@ -779,27 +835,81 @@
       <c r="A17" t="str">
         <v>TOTAL: Sufficient Items (CAD)</v>
       </c>
+      <c r="B17" t="str">
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
       <c r="G17">
         <f>SUM(G5:G16)</f>
-        <v>563.89</v>
+        <v>546.36</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
         <v>HST 13% (CAD)</v>
       </c>
+      <c r="B18" t="str">
+        <v/>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
       <c r="G18">
         <f>ROUND(G17*0.13,2)</f>
-        <v>73.31</v>
+        <v>71.03</v>
+      </c>
+      <c r="H18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
         <v>GRAND TOTAL (CAD)</v>
       </c>
+      <c r="B19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
       <c r="G19">
         <f>G17+G18</f>
-        <v>637.2</v>
+        <v>617.39</v>
+      </c>
+      <c r="H19" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -812,21 +922,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H22"/>
-  <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="55.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="70.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
-    <col min="8" max="8" width="80.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Great</v>
       </c>
+      <c r="B1" t="str">
+        <v/>
+      </c>
+      <c r="C1" t="str">
+        <v/>
+      </c>
+      <c r="D1" t="str">
+        <v/>
+      </c>
+      <c r="E1" t="str">
+        <v/>
+      </c>
+      <c r="F1" t="str">
+        <v/>
+      </c>
+      <c r="G1" t="str">
+        <v/>
+      </c>
+      <c r="H1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -835,6 +956,50 @@
       <c r="B2" t="str">
         <v>2026-02-28</v>
       </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v/>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -913,7 +1078,7 @@
         <v>20.4</v>
       </c>
       <c r="H6" t="str">
-        <v>Exact ST/SC serial bus board for the leader arm.</v>
+        <v>Exact repo board ASIN. LeRobot requires ST/SC serial bus support and B-channel jumpers during setup. Official board docs list 9-12.6V input, which conflicts with the repo's 5V leader PSU guidance.</v>
       </c>
     </row>
     <row r="7">
@@ -948,26 +1113,26 @@
         <v>Leader</v>
       </c>
       <c r="B8" t="str">
-        <v>5V 5A Power Adapter 25W AC 100-240V to DC Wall Power Supply Converter with 5.5x2.5mm/2.1mm Plug</v>
+        <v>Facmogu DC 5V 4A AC to DC Converter, AC 100-240V to DC 5 Volt 4 Amp 20W Power Supply 5V Switching Transformer Power Adapter, Wall Mounted Adapter with with Barrel Connector 5.5x2.5mm &amp; 5.5x2.1mm</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="str">
-        <v>https://www.amazon.ca/MTDZKJG-100-240V-Converter-5-5x2-5mm-Security/dp/B0CJHQNFMG</v>
+        <v>https://www.amazon.ca/Facmogu-Switching-Transformer-Converter-Compatible/dp/B087LY41PV</v>
       </c>
       <c r="E8">
-        <v>26.41</v>
+        <v>14.39</v>
       </c>
       <c r="F8">
-        <v>5.51</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <f>C8*E8+F8</f>
-        <v>31.92</v>
+        <v>14.39</v>
       </c>
       <c r="H8" t="str">
-        <v>Leader-side power supply with 5.5x2.1mm compatibility.</v>
+        <v>Exact SO-101 repo PSU ASIN. Upstream controller-board voltage guidance conflicts with the repo's 5V leader supply recommendation.</v>
       </c>
     </row>
     <row r="9">
@@ -994,7 +1159,7 @@
         <v>199.77</v>
       </c>
       <c r="H9" t="str">
-        <v>Buy 3 packs to get the 6x 12V follower servos required for the shared 12V rail.</v>
+        <v>Buy 3 packs to get the 6x 12V follower servos required for the shared 12V rail. Listing explicitly says 2 servos; accessory/cable contents are not explicit.</v>
       </c>
     </row>
     <row r="10">
@@ -1021,7 +1186,7 @@
         <v>20.4</v>
       </c>
       <c r="H10" t="str">
-        <v>Exact ST/SC serial bus board for the follower arm.</v>
+        <v>Exact repo board ASIN. Set jumpers to B-channel (USB) during LeRobot motor setup. Works with ST/SC serial bus servos.</v>
       </c>
     </row>
     <row r="11">
@@ -1102,7 +1267,7 @@
         <v>7.33</v>
       </c>
       <c r="H13" t="str">
-        <v>Arm hardware fill-in for M2x6 requirements.</v>
+        <v>Matches LeRobot's M2x6 requirement for the arms. Two-arm build needs about 47 M2x6 screws from the HF assembly steps.</v>
       </c>
     </row>
     <row r="14">
@@ -1129,7 +1294,7 @@
         <v>10.49</v>
       </c>
       <c r="H14" t="str">
-        <v>Arm hardware fill-in including M3x6 screws.</v>
+        <v>Current Amazon-only placeholder. Local LeRobot assembly docs call for M3x6 pan-head screws; this row is not an exact head-type match.</v>
       </c>
     </row>
     <row r="15">
@@ -1210,7 +1375,7 @@
         <v>66.28</v>
       </c>
       <c r="H17" t="str">
-        <v>Exact wrist camera row from the SO-101 optional camera docs. Shipping shown once on the listing page.</v>
+        <v>Exact SO-101 wrist-camera module model from the local optional arm docs. This is not the camera family used in LeKiwi's base-camera mount instructions.</v>
       </c>
     </row>
     <row r="18">
@@ -1237,7 +1402,7 @@
         <v>29.99</v>
       </c>
       <c r="H18" t="str">
-        <v>Overhead workspace camera.</v>
+        <v>Amazon.ca substitute. The local SO-101 overhead-webcam doc recommends ASIN B082X91MPP, but I could not recover a live CAD sell price from that listing.</v>
       </c>
     </row>
     <row r="19">
@@ -1271,27 +1436,81 @@
       <c r="A20" t="str">
         <v>TOTAL: Great Items (CAD)</v>
       </c>
+      <c r="B20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
       <c r="G20">
         <f>SUM(G5:G19)</f>
-        <v>670.25</v>
+        <v>652.72</v>
+      </c>
+      <c r="H20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v>HST 13% (CAD)</v>
       </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
       <c r="G21">
         <f>ROUND(G20*0.13,2)</f>
-        <v>87.13</v>
+        <v>84.85</v>
+      </c>
+      <c r="H21" t="str">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
         <v>GRAND TOTAL (CAD)</v>
       </c>
+      <c r="B22" t="str">
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
       <c r="G22">
         <f>G20+G21</f>
-        <v>757.38</v>
+        <v>737.57</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1304,21 +1523,32 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H35"/>
-  <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="55.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="70.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
-    <col min="8" max="8" width="80.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Future</v>
       </c>
+      <c r="B1" t="str">
+        <v/>
+      </c>
+      <c r="C1" t="str">
+        <v/>
+      </c>
+      <c r="D1" t="str">
+        <v/>
+      </c>
+      <c r="E1" t="str">
+        <v/>
+      </c>
+      <c r="F1" t="str">
+        <v/>
+      </c>
+      <c r="G1" t="str">
+        <v/>
+      </c>
+      <c r="H1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -1327,6 +1557,50 @@
       <c r="B2" t="str">
         <v>2026-02-28</v>
       </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v/>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -1405,7 +1679,7 @@
         <v>20.4</v>
       </c>
       <c r="H6" t="str">
-        <v>Exact ST/SC serial bus board for the leader arm.</v>
+        <v>Exact repo board ASIN. LeRobot requires ST/SC serial bus support and B-channel jumpers during setup. Official board docs list 9-12.6V input, which conflicts with the repo's 5V leader PSU guidance.</v>
       </c>
     </row>
     <row r="7">
@@ -1440,26 +1714,26 @@
         <v>Leader</v>
       </c>
       <c r="B8" t="str">
-        <v>5V 5A Power Adapter 25W AC 100-240V to DC Wall Power Supply Converter with 5.5x2.5mm/2.1mm Plug</v>
+        <v>Facmogu DC 5V 4A AC to DC Converter, AC 100-240V to DC 5 Volt 4 Amp 20W Power Supply 5V Switching Transformer Power Adapter, Wall Mounted Adapter with with Barrel Connector 5.5x2.5mm &amp; 5.5x2.1mm</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="str">
-        <v>https://www.amazon.ca/MTDZKJG-100-240V-Converter-5-5x2-5mm-Security/dp/B0CJHQNFMG</v>
+        <v>https://www.amazon.ca/Facmogu-Switching-Transformer-Converter-Compatible/dp/B087LY41PV</v>
       </c>
       <c r="E8">
-        <v>26.41</v>
+        <v>14.39</v>
       </c>
       <c r="F8">
-        <v>5.51</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <f>C8*E8+F8</f>
-        <v>31.92</v>
+        <v>14.39</v>
       </c>
       <c r="H8" t="str">
-        <v>Leader-side power supply with 5.5x2.1mm compatibility.</v>
+        <v>Exact SO-101 repo PSU ASIN. Upstream controller-board voltage guidance conflicts with the repo's 5V leader supply recommendation.</v>
       </c>
     </row>
     <row r="9">
@@ -1486,7 +1760,7 @@
         <v>199.77</v>
       </c>
       <c r="H9" t="str">
-        <v>Buy 3 packs to get the 6x 12V follower servos required for the shared 12V rail.</v>
+        <v>Buy 3 packs to get the 6x 12V follower servos required for the shared 12V rail. Listing explicitly says 2 servos; accessory/cable contents are not explicit.</v>
       </c>
     </row>
     <row r="10">
@@ -1513,7 +1787,7 @@
         <v>20.4</v>
       </c>
       <c r="H10" t="str">
-        <v>Exact ST/SC serial bus board for the follower arm.</v>
+        <v>Exact repo board ASIN. Set jumpers to B-channel (USB) during LeRobot motor setup. Works with ST/SC serial bus servos.</v>
       </c>
     </row>
     <row r="11">
@@ -1594,7 +1868,7 @@
         <v>7.33</v>
       </c>
       <c r="H13" t="str">
-        <v>Arm hardware fill-in for M2x6 requirements.</v>
+        <v>Matches LeRobot's M2x6 requirement for the arms. Two-arm build needs about 47 M2x6 screws from the HF assembly steps.</v>
       </c>
     </row>
     <row r="14">
@@ -1621,7 +1895,7 @@
         <v>10.49</v>
       </c>
       <c r="H14" t="str">
-        <v>Arm hardware fill-in including M3x6 screws.</v>
+        <v>Current Amazon-only placeholder. Local LeRobot assembly docs call for M3x6 pan-head screws; this row is not an exact head-type match.</v>
       </c>
     </row>
     <row r="15">
@@ -1702,7 +1976,7 @@
         <v>66.28</v>
       </c>
       <c r="H17" t="str">
-        <v>Exact wrist camera row from the SO-101 optional camera docs. Shipping shown once on the listing page.</v>
+        <v>Exact SO-101 wrist-camera module model from the local optional arm docs. This is not the camera family used in LeKiwi's base-camera mount instructions.</v>
       </c>
     </row>
     <row r="18">
@@ -1729,7 +2003,7 @@
         <v>29.99</v>
       </c>
       <c r="H18" t="str">
-        <v>Overhead workspace camera.</v>
+        <v>Amazon.ca substitute. The local SO-101 overhead-webcam doc recommends ASIN B082X91MPP, but I could not recover a live CAD sell price from that listing.</v>
       </c>
     </row>
     <row r="19">
@@ -1783,7 +2057,7 @@
         <v>122.64</v>
       </c>
       <c r="H20" t="str">
-        <v>Amazon-only 100mm omni wheel option for LeKiwi. Not the VEX wheel from the original LeKiwi BOM.</v>
+        <v>Amazon-only substitute. LeKiwi's BOM references a VEX 4-inch omni wheel, not this exact Amazon.ca wheel.</v>
       </c>
     </row>
     <row r="21">
@@ -1810,7 +2084,7 @@
         <v>66.59</v>
       </c>
       <c r="H21" t="str">
-        <v>One 2-pack for two of the three LeKiwi base drive servos.</v>
+        <v>One 2-pack for two of the three LeKiwi base drive servos. Listing explicitly says 2 servos; accessory/cable contents are not explicit.</v>
       </c>
     </row>
     <row r="22">
@@ -1837,7 +2111,7 @@
         <v>45.97</v>
       </c>
       <c r="H22" t="str">
-        <v>Single 12V STS3215 to complete the 3-servo LeKiwi base drive set.</v>
+        <v>Single 12V STS3215 to complete the 3-servo LeKiwi base drive set. Listing explicitly says 1 servo; accessory/cable contents are not explicit.</v>
       </c>
     </row>
     <row r="23">
@@ -2026,7 +2300,7 @@
         <v>28.99</v>
       </c>
       <c r="H29" t="str">
-        <v>Base hardware assortment covering M2/M3/M4 needs.</v>
+        <v>Cheaper Amazon.ca substitute for LeKiwi's assorted base screw row. Covers many base machine-screw sizes, but not the arm's exact M2.5 board-mount hardware.</v>
       </c>
     </row>
     <row r="30">
@@ -2114,27 +2388,81 @@
       <c r="A33" t="str">
         <v>TOTAL: Future Items (CAD)</v>
       </c>
+      <c r="B33" t="str">
+        <v/>
+      </c>
+      <c r="C33" t="str">
+        <v/>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
       <c r="G33">
         <f>SUM(G5:G32)</f>
-        <v>1288.43</v>
+        <v>1270.9</v>
+      </c>
+      <c r="H33" t="str">
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
         <v>HST 13% (CAD)</v>
       </c>
+      <c r="B34" t="str">
+        <v/>
+      </c>
+      <c r="C34" t="str">
+        <v/>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
       <c r="G34">
         <f>ROUND(G33*0.13,2)</f>
-        <v>167.5</v>
+        <v>165.22</v>
+      </c>
+      <c r="H34" t="str">
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
         <v>GRAND TOTAL (CAD)</v>
       </c>
+      <c r="B35" t="str">
+        <v/>
+      </c>
+      <c r="C35" t="str">
+        <v/>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
       <c r="G35">
         <f>G33+G34</f>
-        <v>1455.93</v>
+        <v>1436.12</v>
+      </c>
+      <c r="H35" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2147,13 +2475,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E6"/>
-  <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="55.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2183,18 +2504,18 @@
       </c>
       <c r="B4">
         <f>Sufficient!G17</f>
-        <v>563.89</v>
+        <v>546.36</v>
       </c>
       <c r="C4">
         <f>Sufficient!G18</f>
-        <v>73.31</v>
+        <v>71.03</v>
       </c>
       <c r="D4">
         <f>Sufficient!G19</f>
-        <v>637.2</v>
+        <v>617.39</v>
       </c>
       <c r="E4" t="str">
-        <v>Core dual-arm teleop build without cameras or base.</v>
+        <v>Core dual-arm teleop build. Does not include unresolved board-mount hardware.</v>
       </c>
     </row>
     <row r="5">
@@ -2203,18 +2524,18 @@
       </c>
       <c r="B5">
         <f>Great!G20</f>
-        <v>670.25</v>
+        <v>652.72</v>
       </c>
       <c r="C5">
         <f>Great!G21</f>
-        <v>87.13</v>
+        <v>84.85</v>
       </c>
       <c r="D5">
         <f>Great!G22</f>
-        <v>757.38</v>
+        <v>737.57</v>
       </c>
       <c r="E5" t="str">
-        <v>Adds cameras and grip tape for better teleop and data collection.</v>
+        <v>Adds SO-101 camera options and grip tape. LeKiwi-specific camera mounts are not covered here.</v>
       </c>
     </row>
     <row r="6">
@@ -2223,18 +2544,18 @@
       </c>
       <c r="B6">
         <f>Future!G33</f>
-        <v>1288.43</v>
+        <v>1270.9</v>
       </c>
       <c r="C6">
         <f>Future!G34</f>
-        <v>167.5</v>
+        <v>165.22</v>
       </c>
       <c r="D6">
         <f>Future!G35</f>
-        <v>1455.93</v>
+        <v>1436.12</v>
       </c>
       <c r="E6" t="str">
-        <v>Adds the LeKiwi follower base and onboard compute.</v>
+        <v>Adds LeKiwi base items, but still excludes unresolved M2.5 board-mount hardware and M2x5 tap screws.</v>
       </c>
     </row>
   </sheetData>
@@ -2242,4 +2563,222 @@
     <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D15"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="120.83203125" customWidth="1"/>
+    <col min="4" max="4" width="70.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Audit</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Status</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Scope</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Detail</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Source</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Confirmed</v>
+      </c>
+      <c r="B3" t="str">
+        <v>SO-101 motors</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Leader gear split is 3x C046 + 2x C044 + 1x C001; standard follower is 6x C001; 12V follower upgrade must keep all 6 follower servos on the 12V rail.</v>
+      </c>
+      <c r="D3" t="str">
+        <v>README.md:70; README.md:76; README.md:77; README.md:78; README.md:93</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Confirmed</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Arm fasteners</v>
+      </c>
+      <c r="C4" t="str">
+        <v>LeRobot HF assembly uses M2x6 and M3x6 throughout the SO-101 arm. Two-arm build is roughly 47x M2x6 and 87x M3x6 from the published steps.</v>
+      </c>
+      <c r="D4" t="str">
+        <v>huggingface/lerobot docs/source/so101.mdx</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Missing</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Board mount hardware</v>
+      </c>
+      <c r="C5" t="str">
+        <v>The SO-101 STEP assembly includes 4x M2.5x4 pan-head screws and 4x M2.5 spacers for the bus-servo board mount. Those are not in the repo BOM and the Amazon board listing package text only says Bus Servo Adapter x1.</v>
+      </c>
+      <c r="D5" t="str">
+        <v>STEP/SO101/SO101 Assembly.step; Amazon B0CTMM4LWK</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Mismatch</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Leader power path</v>
+      </c>
+      <c r="C6" t="str">
+        <v>The repo BOM pairs the board with a 5V PSU for the leader, but the Amazon board description says 9-12.6V input should match servo voltage. This is an upstream source conflict I could not fully resolve.</v>
+      </c>
+      <c r="D6" t="str">
+        <v>README.md:79; README.md:81; Amazon B0CTMM4LWK</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Mismatch</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Arm M3 screws</v>
+      </c>
+      <c r="C7" t="str">
+        <v>The current Amazon-only arm M3 row is not an exact pan-head match. The local HF assembly steps call for M3x6 screws, and the local STEP model names them as pan-head.</v>
+      </c>
+      <c r="D7" t="str">
+        <v>lerobot so101 docs; STEP/SO101/SO101 Assembly.step</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Risk</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Servo accessories</v>
+      </c>
+      <c r="C8" t="str">
+        <v>The 12V Amazon servo listings explicitly describe servo quantities but do not explicitly enumerate accessory bags. Cable/horn inclusion is therefore assumed, not confirmed from the listing text.</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Amazon B0FVS5HD2V; Amazon B0FGNTDV3Y</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Risk</v>
+      </c>
+      <c r="B9" t="str">
+        <v>LeKiwi base cameras</v>
+      </c>
+      <c r="C9" t="str">
+        <v>The current workbook cameras match SO-101 wrist-camera docs, not LeKiwi's documented base-camera mount families. For exact LeKiwi camera mounts, the repo points to Arducam or Vinmooog-style cameras instead.</v>
+      </c>
+      <c r="D9" t="str">
+        <v>LeKiwi Assembly.md; Optional/Wrist_Cam_Mount_32x32_UVC_Module/README.md</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Missing</v>
+      </c>
+      <c r="B10" t="str">
+        <v>LeKiwi tap screws</v>
+      </c>
+      <c r="C10" t="str">
+        <v>LeKiwi assembly explicitly calls for M2x5 tap screws for each wheel module. Those are not separately sourced in the current Amazon-only workbook.</v>
+      </c>
+      <c r="D10" t="str">
+        <v>LeKiwi Assembly.md</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Totals</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Current workbook</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Displayed totals are formula-backed and cached, but they still exclude the unresolved M2.5 board-mount hardware and any unresolved LeKiwi camera-mount hardware.</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Robot Arm Parts.xlsx</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Total</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Lowest</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Total</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Sufficient</v>
+      </c>
+      <c r="C13">
+        <v>617.39</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Total</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Great</v>
+      </c>
+      <c r="C14">
+        <v>737.57</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Total</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Future</v>
+      </c>
+      <c r="C15">
+        <v>1436.12</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D15"/>
+  </ignoredErrors>
+</worksheet>
 </file>